--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484143_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484143_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9375</v>
+        <v>1.7117</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6369</v>
+        <v>2.4951</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6993</v>
+        <v>-0.7835</v>
       </c>
       <c r="G2" t="n">
         <v>4.1965</v>
@@ -610,13 +610,13 @@
         <v>0.5952</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5163</v>
+        <v>0.2905</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1814</v>
+        <v>0.0397</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3349</v>
+        <v>0.2507</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9899</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2432</v>
+        <v>1.628</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0077</v>
+        <v>0.321</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2509</v>
+        <v>1.307</v>
       </c>
       <c r="G3" t="n">
         <v>2.8779</v>
@@ -688,13 +688,13 @@
         <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4363</v>
+        <v>-1.0515</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.6688</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4388</v>
+        <v>-0.3827</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. MARTÍN LLAVERÍA</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6491</v>
+        <v>1.0907</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3558</v>
+        <v>3.1539</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2933</v>
+        <v>-2.0632</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5493</v>
+        <v>1.3743</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1515</v>
+        <v>2.162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7009</v>
+        <v>-0.7877</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6051</v>
+        <v>2.8712</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0403</v>
+        <v>2.344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5648</v>
+        <v>0.5272</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0558</v>
+        <v>-1.497</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1918</v>
+        <v>-0.1821</v>
       </c>
       <c r="O4" t="n">
-        <v>0.136</v>
+        <v>-1.3149</v>
       </c>
       <c r="P4" t="n">
         <v>0.5952</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.3968</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5952</v>
+        <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4954</v>
+        <v>-0.7581</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2494</v>
+        <v>-0.5271</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.246</v>
+        <v>-0.2311</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.1206</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.3271</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>L. MARTÍN LLAVERÍA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5423</v>
+        <v>0.7052</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7458</v>
+        <v>0.3558</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2035</v>
+        <v>0.3494</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3743</v>
+        <v>0.5493</v>
       </c>
       <c r="H5" t="n">
-        <v>2.162</v>
+        <v>-0.1515</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7877</v>
+        <v>0.7009</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8712</v>
+        <v>0.6051</v>
       </c>
       <c r="K5" t="n">
-        <v>2.344</v>
+        <v>0.0403</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5272</v>
+        <v>0.5648</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.497</v>
+        <v>-0.0558</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1821</v>
+        <v>-0.1918</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3149</v>
+        <v>0.136</v>
       </c>
       <c r="P5" t="n">
         <v>0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.3968</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.3065</v>
+        <v>-0.4393</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9352</v>
+        <v>-0.2494</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3713</v>
+        <v>-0.1899</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1206</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.3271</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. MORENO MARTIN</t>
+          <t>B. BONET TORRALBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0478</v>
+        <v>0.0506</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8998</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.852</v>
+        <v>0.0603</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0475</v>
+        <v>-1.0811</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1965</v>
+        <v>-2.4039</v>
       </c>
       <c r="I6" t="n">
-        <v>0.149</v>
+        <v>1.3228</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5391</v>
+        <v>0.096</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5391</v>
+        <v>-1.3498</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.4458</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4916</v>
+        <v>-1.1772</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3425</v>
+        <v>-1.0541</v>
       </c>
       <c r="O6" t="n">
-        <v>0.149</v>
+        <v>-0.123</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3968</v>
+        <v>1.5871</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0176</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4308</v>
+        <v>0.0171</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4132</v>
+        <v>-0.0837</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1206</v>
+        <v>0.6032</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2065</v>
+        <v>0.8692</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3271</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. BONET TORRALBA</t>
+          <t>P. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0624</v>
+        <v>-0.1639</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0946</v>
+        <v>0.4917</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0322</v>
+        <v>-0.6556</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0811</v>
+        <v>-0.0475</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4039</v>
+        <v>-0.1965</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3228</v>
+        <v>0.149</v>
       </c>
       <c r="J7" t="n">
-        <v>0.096</v>
+        <v>-0.5391</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.3498</v>
+        <v>-0.5391</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4458</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1772</v>
+        <v>0.4916</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0541</v>
+        <v>0.3425</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.123</v>
+        <v>0.149</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>-0.1984</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5871</v>
+        <v>0.3968</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1797</v>
+        <v>-0.1941</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0679</v>
+        <v>0.0227</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1117</v>
+        <v>-0.2168</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6032</v>
+        <v>-0.1206</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8692</v>
+        <v>1.2065</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.266</v>
+        <v>-1.3271</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2142</v>
+        <v>-0.4455</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8666</v>
+        <v>-0.9857</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6524</v>
+        <v>0.5402</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5135</v>
@@ -1078,13 +1078,13 @@
         <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2993</v>
+        <v>0.068</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0056</v>
+        <v>-0.1247</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3049</v>
+        <v>0.1926</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DIEZ VALERO</t>
+          <t>E. NOGUES MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4914</v>
+        <v>-1.4293</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5747</v>
+        <v>-1.3206</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0833</v>
+        <v>-0.1087</v>
       </c>
       <c r="G9" t="n">
-        <v>1.1737</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0261</v>
+        <v>1.315</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8524</v>
+        <v>-2.2349</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9281</v>
+        <v>0.8935</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2082</v>
+        <v>1.684</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2801</v>
+        <v>-0.7905</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2455</v>
+        <v>-1.8135</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1821</v>
+        <v>-0.369</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4276</v>
+        <v>-1.4444</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.579</v>
+        <v>0.1984</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.3725</v>
+        <v>-2.1822</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7935</v>
+        <v>2.3806</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0345</v>
+        <v>-1.5276</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1303</v>
+        <v>-0.9011</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1648</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1206</v>
+        <v>0.8198</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1206</v>
+        <v>-0.0494</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. NOGUES MARTIN</t>
+          <t>A. DIEZ VALERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8436</v>
+        <v>-1.655</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7911</v>
+        <v>-2.654</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0526</v>
+        <v>0.9991</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9199000000000001</v>
+        <v>1.1737</v>
       </c>
       <c r="H10" t="n">
-        <v>1.315</v>
+        <v>2.0261</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.2349</v>
+        <v>-0.8524</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8935</v>
+        <v>0.9281</v>
       </c>
       <c r="K10" t="n">
-        <v>1.684</v>
+        <v>2.2082</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7905</v>
+        <v>-1.2801</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8135</v>
+        <v>0.2455</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.369</v>
+        <v>-0.1821</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4444</v>
+        <v>0.4276</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1984</v>
+        <v>-2.579</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1822</v>
+        <v>-3.3725</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3806</v>
+        <v>0.7935</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.942</v>
+        <v>-0.129</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3716</v>
+        <v>-0.2097</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5704</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8198</v>
+        <v>-0.1206</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.0494</v>
+        <v>-0.1206</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8692</v>
+        <v>-1.7751</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0683</v>
+        <v>-1.6376</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1991</v>
+        <v>-0.1375</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1265</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0124</v>
+        <v>-0.9183</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1222</v>
+        <v>-0.6914</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1098</v>
+        <v>-0.2268</v>
       </c>
       <c r="V11" t="n">
         <v>0.0713</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2729</v>
+        <v>-3.681</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7988</v>
+        <v>-2.2069</v>
       </c>
       <c r="F12" t="n">
         <v>-1.4741</v>
@@ -1390,10 +1390,10 @@
         <v>0.1984</v>
       </c>
       <c r="S12" t="n">
+        <v>-0.3231</v>
+      </c>
+      <c r="T12" t="n">
         <v>0.08500000000000001</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.4932</v>
       </c>
       <c r="U12" t="n">
         <v>-0.4081</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.4334</v>
+        <v>-4.8686</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8138</v>
+        <v>-2.4454</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6195</v>
+        <v>-2.4232</v>
       </c>
       <c r="G13" t="n">
         <v>-4.1279</v>
@@ -1468,13 +1468,13 @@
         <v>1.1903</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6942</v>
+        <v>-1.1294</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8728</v>
+        <v>-0.5044</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8213</v>
+        <v>-0.625</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6032</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.767199999999999</v>
+        <v>-8.8322</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.3773</v>
+        <v>-4.442299999999999</v>
       </c>
       <c r="F14" t="n">
         <v>-4.3898</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05689999999999973</v>
+        <v>0.05690000000000062</v>
       </c>
       <c r="H14" t="n">
         <v>4.1057</v>
@@ -1519,7 +1519,7 @@
         <v>-4.0487</v>
       </c>
       <c r="J14" t="n">
-        <v>9.730899999999998</v>
+        <v>9.7309</v>
       </c>
       <c r="K14" t="n">
         <v>8.5983</v>
@@ -1546,13 +1546,13 @@
         <v>12.8951</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.113799999999999</v>
+        <v>-6.1785</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.6471</v>
+        <v>-3.7121</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.4664</v>
+        <v>-2.4666</v>
       </c>
       <c r="V14" t="n">
         <v>-0.7266</v>
@@ -1561,7 +1561,7 @@
         <v>4.4174</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.144000000000001</v>
+        <v>-5.144</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.8273</v>
+        <v>7.4651</v>
       </c>
       <c r="E15" t="n">
-        <v>6.954</v>
+        <v>6.6479</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8733</v>
+        <v>0.8172</v>
       </c>
       <c r="G15" t="n">
         <v>5.0436</v>
@@ -1624,13 +1624,13 @@
         <v>2.1822</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7198</v>
+        <v>1.3576</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0658</v>
+        <v>0.7597</v>
       </c>
       <c r="U15" t="n">
-        <v>0.654</v>
+        <v>0.5979</v>
       </c>
       <c r="V15" t="n">
         <v>1.0639</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. MARRÓN ROSA</t>
+          <t>P. PARISI TRIA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9436</v>
+        <v>4.1753</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2703</v>
+        <v>3.3017</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6733</v>
+        <v>0.8736</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5603</v>
+        <v>0.5593</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7872</v>
+        <v>-1.2299</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.2269</v>
+        <v>1.7892</v>
       </c>
       <c r="J16" t="n">
-        <v>3.126</v>
+        <v>1.3988</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8413</v>
+        <v>0.0308</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7153</v>
+        <v>1.368</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.5658</v>
+        <v>-0.8395</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0541</v>
+        <v>-1.2606</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5117</v>
+        <v>0.4211</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3887</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9838</v>
+        <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0542</v>
+        <v>0.2905</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9297</v>
+        <v>0.1645</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1245</v>
+        <v>0.1261</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.266</v>
+        <v>1.7384</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6032</v>
+        <v>1.7384</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. PARISI TRIA</t>
+          <t>P. MARRÓN ROSA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4025</v>
+        <v>3.4794</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8936</v>
+        <v>2.8622</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5089</v>
+        <v>0.6172</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5593</v>
+        <v>1.5603</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2299</v>
+        <v>2.7872</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7892</v>
+        <v>-1.2269</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3988</v>
+        <v>3.126</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0308</v>
+        <v>3.8413</v>
       </c>
       <c r="L17" t="n">
-        <v>1.368</v>
+        <v>-0.7153</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8395</v>
+        <v>-1.5658</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2606</v>
+        <v>-1.0541</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4211</v>
+        <v>-0.5117</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5871</v>
+        <v>0.5952</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.3887</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5871</v>
+        <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4823</v>
+        <v>1.5899</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2436</v>
+        <v>0.5216</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2387</v>
+        <v>1.0683</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7384</v>
+        <v>-0.266</v>
       </c>
       <c r="W17" t="n">
-        <v>1.7384</v>
+        <v>0.6032</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0288</v>
+        <v>2.0187</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5963</v>
+        <v>1.474</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4325</v>
+        <v>0.5447</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1583</v>
@@ -1858,13 +1858,13 @@
         <v>1.5871</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2628</v>
+        <v>1.2527</v>
       </c>
       <c r="T18" t="n">
-        <v>2.12</v>
+        <v>0.9977</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1428</v>
+        <v>0.255</v>
       </c>
       <c r="V18" t="n">
         <v>-0.266</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7086</v>
+        <v>1.5964</v>
       </c>
       <c r="E19" t="n">
         <v>1.1405</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5681</v>
+        <v>0.4559</v>
       </c>
       <c r="G19" t="n">
         <v>1.1996</v>
@@ -1936,13 +1936,13 @@
         <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1122</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1247</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2369</v>
+        <v>0.1247</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8688</v>
+        <v>0.6273</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1546</v>
+        <v>-1.3586</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0233</v>
+        <v>1.9859</v>
       </c>
       <c r="G20" t="n">
         <v>0.6018</v>
@@ -2014,13 +2014,13 @@
         <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8621</v>
+        <v>0.6207</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2551</v>
+        <v>0.0511</v>
       </c>
       <c r="U20" t="n">
-        <v>0.607</v>
+        <v>0.5696</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1708</v>
+        <v>0.5203</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7926</v>
+        <v>-1.0784</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9635</v>
+        <v>1.5988</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8443</v>
@@ -2092,13 +2092,13 @@
         <v>2.3806</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2216</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7254</v>
+        <v>-0.0112</v>
       </c>
       <c r="U21" t="n">
-        <v>0.947</v>
+        <v>0.5823</v>
       </c>
       <c r="V21" t="n">
         <v>0.6032</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8103</v>
+        <v>-1.318</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2583</v>
+        <v>-0.8502</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.4678</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0219</v>
@@ -2170,13 +2170,13 @@
         <v>0.3968</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1933</v>
+        <v>0.299</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3117</v>
+        <v>0.0964</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1185</v>
+        <v>0.2026</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2409</v>
+        <v>-1.8813</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9213</v>
+        <v>-2.3091</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6803</v>
+        <v>0.4278</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5653</v>
@@ -2248,13 +2248,13 @@
         <v>0.7935</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4551</v>
+        <v>0.8148</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6121</v>
+        <v>0.0001</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0672</v>
+        <v>0.8147</v>
       </c>
       <c r="V23" t="n">
         <v>0.266</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1625</v>
+        <v>-2.91</v>
       </c>
       <c r="E24" t="n">
         <v>-2.6524</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5101</v>
+        <v>-0.2576</v>
       </c>
       <c r="G24" t="n">
         <v>-1.8402</v>
@@ -2326,13 +2326,13 @@
         <v>1.3887</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3304</v>
+        <v>-0.0779</v>
       </c>
       <c r="T24" t="n">
         <v>-0.0056</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3248</v>
+        <v>-0.0723</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9695</v>
+        <v>-3.9593</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.6857</v>
+        <v>-2.7877</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2838</v>
+        <v>-1.1716</v>
       </c>
       <c r="G25" t="n">
         <v>-1.5917</v>
@@ -2404,13 +2404,13 @@
         <v>0.7935</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4319</v>
+        <v>0.4421</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1191</v>
+        <v>0.0171</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3128</v>
+        <v>0.4251</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4129</v>
@@ -2437,34 +2437,34 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>9.767200000000001</v>
+        <v>9.8139</v>
       </c>
       <c r="E26" t="n">
-        <v>4.389799999999999</v>
+        <v>4.389899999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>5.377399999999999</v>
+        <v>5.4241</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.05710000000000082</v>
+        <v>-0.05709999999999993</v>
       </c>
       <c r="H26" t="n">
         <v>-4.105700000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>4.048599999999999</v>
+        <v>4.0486</v>
       </c>
       <c r="J26" t="n">
         <v>9.674300000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>4.492800000000001</v>
+        <v>4.4928</v>
       </c>
       <c r="L26" t="n">
         <v>5.181400000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-9.731100000000001</v>
+        <v>-9.7311</v>
       </c>
       <c r="N26" t="n">
         <v>-8.5983</v>
@@ -2482,13 +2482,13 @@
         <v>14.8788</v>
       </c>
       <c r="S26" t="n">
-        <v>7.1137</v>
+        <v>7.160500000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4666</v>
+        <v>2.4667</v>
       </c>
       <c r="U26" t="n">
-        <v>4.647200000000001</v>
+        <v>4.693999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>0.7265999999999999</v>
